--- a/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
+++ b/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
@@ -1,23 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2660DC46-0FC8-4BA0-A79C-49C5CB2A1260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB0788B-E3E8-4A0F-96FB-6537B312536E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Сделка" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,30 +25,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="105">
   <si>
     <t>СДЕЛКА</t>
   </si>
@@ -88,21 +58,27 @@
     <t>Количество собственников</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Стоимость USD</t>
   </si>
   <si>
+    <t>105000</t>
+  </si>
+  <si>
     <t>Стоимость BYN</t>
   </si>
   <si>
-    <t>Стоимость прописью</t>
-  </si>
-  <si>
     <t>Комиссия агентства</t>
   </si>
   <si>
     <t>3500 BYN</t>
   </si>
   <si>
+    <t>Ответственный риэлтер</t>
+  </si>
+  <si>
     <t>Ольга Турко</t>
   </si>
   <si>
@@ -127,12 +103,6 @@
     <t>Лида</t>
   </si>
   <si>
-    <t>Район</t>
-  </si>
-  <si>
-    <t>Центр</t>
-  </si>
-  <si>
     <t>Улица</t>
   </si>
   <si>
@@ -154,21 +124,36 @@
     <t>Этаж</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>Этажность</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>Количество комнат</t>
   </si>
   <si>
     <t>Общая площадь</t>
   </si>
   <si>
+    <t>63.2</t>
+  </si>
+  <si>
     <t>Жилая площадь</t>
   </si>
   <si>
+    <t>39.8</t>
+  </si>
+  <si>
     <t>Площадь кухни</t>
   </si>
   <si>
+    <t>8.7</t>
+  </si>
+  <si>
     <t>Кадастровый номер</t>
   </si>
   <si>
@@ -250,12 +235,6 @@
     <t>+375291112233</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>petrov@example.by</t>
-  </si>
-  <si>
     <t>Является собственником</t>
   </si>
   <si>
@@ -301,30 +280,6 @@
     <t>СОБСТВЕННИК №2</t>
   </si>
   <si>
-    <t>Иванова</t>
-  </si>
-  <si>
-    <t>Мария</t>
-  </si>
-  <si>
-    <t>Петровна</t>
-  </si>
-  <si>
-    <t>17.08.1977</t>
-  </si>
-  <si>
-    <t>7654321</t>
-  </si>
-  <si>
-    <t>4170877A002PB2</t>
-  </si>
-  <si>
-    <t>15.05.2019</t>
-  </si>
-  <si>
-    <t>+375297654321</t>
-  </si>
-  <si>
     <t>СОБСТВЕННИК №3</t>
   </si>
   <si>
@@ -364,7 +319,28 @@
     <t>+375447778899</t>
   </si>
   <si>
-    <t>Ответственный риэлтер</t>
+    <t>Сумма задатка BYN</t>
+  </si>
+  <si>
+    <t>Сумма задатка USD</t>
+  </si>
+  <si>
+    <t>Оплата услуг БТИ</t>
+  </si>
+  <si>
+    <t>50/50</t>
+  </si>
+  <si>
+    <t>Назаров</t>
+  </si>
+  <si>
+    <t>Игорь</t>
+  </si>
+  <si>
+    <t>Валерьевич</t>
+  </si>
+  <si>
+    <t>Нет</t>
   </si>
 </sst>
 </file>
@@ -404,7 +380,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -427,14 +403,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -444,7 +433,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -454,26 +443,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Лист1"/>
-      <sheetName val="Лист2"/>
-      <sheetName val="Лист3"/>
-    </sheetNames>
-    <definedNames>
-      <definedName name="СуммаПрописьюBYN"/>
-    </definedNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -768,11 +737,11 @@
     <col min="2" max="2" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -810,693 +779,690 @@
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2">
-        <v>2</v>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2">
-        <v>103000</v>
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2">
-        <v>330630</v>
+        <v>150450</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="str" cm="1">
-        <f t="array" ref="B9">[1]!СуммаПрописьюBYN(B8)</f>
-        <v>Триста тридцать тысяч шестьсот тридцать белорусских рублей 00 копеек</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="3">
+        <v>400</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B14" s="6"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>30</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B20" s="2"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="2">
-        <v>3</v>
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B22" s="2">
-        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="2">
-        <v>3</v>
+      <c r="B23" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="2">
-        <v>63.2</v>
+        <v>35</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="2">
-        <v>39.799999999999997</v>
+        <v>36</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="2">
-        <v>8.6999999999999993</v>
+        <v>38</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="4"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="2" t="s">
         <v>43</v>
       </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B43" s="2"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B44" s="2"/>
     </row>
-    <row r="45" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45" s="4"/>
+    <row r="45" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" s="6"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B58" s="4"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" s="6"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B71" s="4"/>
+        <v>81</v>
+      </c>
+      <c r="B70" s="2"/>
+    </row>
+    <row r="71" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" s="6"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B72" s="2"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B73" s="2"/>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B74" s="2"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B75" s="2"/>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B76" s="2"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B77" s="2"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B78" s="2"/>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B79" s="2"/>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B80" s="2"/>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B81" s="2"/>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B82" s="2"/>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B83" s="2"/>
     </row>
-    <row r="84" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B84" s="4"/>
+    <row r="84" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" s="6"/>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B5 B42" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="B42 B5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
+++ b/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB0788B-E3E8-4A0F-96FB-6537B312536E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C5EA40-662C-4A9F-A8AC-925A66CE2FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="103">
   <si>
     <t>СДЕЛКА</t>
   </si>
@@ -68,12 +68,6 @@
   </si>
   <si>
     <t>Стоимость BYN</t>
-  </si>
-  <si>
-    <t>Комиссия агентства</t>
-  </si>
-  <si>
-    <t>3500 BYN</t>
   </si>
   <si>
     <t>Ответственный риэлтер</t>
@@ -730,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B95"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -799,7 +793,7 @@
         <v>150450</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -807,43 +801,43 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B13" s="6"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="6"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -881,19 +875,19 @@
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>30</v>
@@ -912,15 +906,15 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -955,19 +949,19 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="B30" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="6"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1054,41 +1048,41 @@
         <v>67</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>104</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B42" s="2"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="2"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="B44" s="6"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="2"/>
-    </row>
-    <row r="45" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B45" s="6"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1096,7 +1090,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1104,7 +1098,7 @@
         <v>51</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1112,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1120,7 +1114,7 @@
         <v>55</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1128,7 +1122,7 @@
         <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1136,7 +1130,7 @@
         <v>59</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1144,7 +1138,7 @@
         <v>61</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1152,7 +1146,7 @@
         <v>63</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1160,37 +1154,37 @@
         <v>65</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B58" s="6"/>
+      <c r="B57" s="6"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -1198,7 +1192,7 @@
         <v>49</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -1206,7 +1200,7 @@
         <v>51</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -1214,7 +1208,7 @@
         <v>53</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -1222,7 +1216,7 @@
         <v>55</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -1230,7 +1224,7 @@
         <v>57</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -1238,7 +1232,7 @@
         <v>59</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -1246,7 +1240,7 @@
         <v>61</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -1254,7 +1248,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -1262,28 +1256,26 @@
         <v>65</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B70" s="2"/>
-    </row>
-    <row r="71" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B71" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="B69" s="2"/>
+    </row>
+    <row r="70" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B70" s="6"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" s="2"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
@@ -1347,28 +1339,30 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B82" s="2"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B83" s="2"/>
-    </row>
-    <row r="84" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B84" s="6"/>
+    <row r="83" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="6"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -1376,7 +1370,7 @@
         <v>49</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -1384,7 +1378,7 @@
         <v>51</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -1392,7 +1386,7 @@
         <v>53</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -1400,7 +1394,7 @@
         <v>55</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -1408,7 +1402,7 @@
         <v>57</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -1416,7 +1410,7 @@
         <v>59</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -1424,7 +1418,7 @@
         <v>61</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -1432,7 +1426,7 @@
         <v>63</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -1440,29 +1434,21 @@
         <v>65</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A83:B83"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A57:B57"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B42 B5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="B41 B5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
+++ b/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
@@ -1,32 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24430"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C5EA40-662C-4A9F-A8AC-925A66CE2FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="Сделка" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Сделка" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
   <si>
     <t>СДЕЛКА</t>
   </si>
@@ -76,6 +64,18 @@
     <t>Ольга Турко</t>
   </si>
   <si>
+    <t>Сумма задатка BYN</t>
+  </si>
+  <si>
+    <t>Сумма задатка USD</t>
+  </si>
+  <si>
+    <t>Оплата услуг БТИ</t>
+  </si>
+  <si>
+    <t>50/50</t>
+  </si>
+  <si>
     <t>ОБЪЕКТ</t>
   </si>
   <si>
@@ -160,6 +160,15 @@
     <t>INV-874521</t>
   </si>
   <si>
+    <t>Материал стен</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Год постройки</t>
+  </si>
+  <si>
     <t>ПРОДАВЕЦ</t>
   </si>
   <si>
@@ -232,6 +241,9 @@
     <t>Является собственником</t>
   </si>
   <si>
+    <t>Нет</t>
+  </si>
+  <si>
     <t>Номер доверенности</t>
   </si>
   <si>
@@ -274,6 +286,15 @@
     <t>СОБСТВЕННИК №2</t>
   </si>
   <si>
+    <t>Назаров</t>
+  </si>
+  <si>
+    <t>Игорь</t>
+  </si>
+  <si>
+    <t>Валерьевич</t>
+  </si>
+  <si>
     <t>СОБСТВЕННИК №3</t>
   </si>
   <si>
@@ -311,48 +332,24 @@
   </si>
   <si>
     <t>+375447778899</t>
-  </si>
-  <si>
-    <t>Сумма задатка BYN</t>
-  </si>
-  <si>
-    <t>Сумма задатка USD</t>
-  </si>
-  <si>
-    <t>Оплата услуг БТИ</t>
-  </si>
-  <si>
-    <t>50/50</t>
-  </si>
-  <si>
-    <t>Назаров</t>
-  </si>
-  <si>
-    <t>Игорь</t>
-  </si>
-  <si>
-    <t>Валерьевич</t>
-  </si>
-  <si>
-    <t>Нет</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -412,19 +409,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -723,732 +718,751 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B94"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B96"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>150450</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>1200</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="1"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="3"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="3"/>
+    </row>
+    <row r="46" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="1"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="59" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B59" s="1"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B71" s="3"/>
+    </row>
+    <row r="72" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" s="3"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="3"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B76" s="3"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B77" s="3"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="3"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="3"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" s="3"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B81" s="3"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B82" s="3"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B83" s="3"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B85" s="1"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="6"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" s="2" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="B90" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" s="2" t="s">
+      <c r="B91" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" s="2" t="s">
+      <c r="B92" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="2" t="s">
+      <c r="B93" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="2"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B43" s="2"/>
-    </row>
-    <row r="44" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
+      <c r="B94" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="6"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="2" t="s">
+      <c r="B95" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B57" s="6"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B69" s="2"/>
-    </row>
-    <row r="70" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B70" s="6"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="2"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B72" s="2"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B73" s="2"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B74" s="2"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B75" s="2"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B76" s="2"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B77" s="2"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B78" s="2"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B79" s="2"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B80" s="2"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B81" s="2"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B82" s="2"/>
-    </row>
-    <row r="83" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B83" s="6"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>94</v>
+      <c r="B96" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A83:B83"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A85:B85"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="B41 B5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="B41">
+      <formula1>"Да,Нет"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B5">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
+++ b/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="107">
   <si>
     <t>СДЕЛКА</t>
   </si>
@@ -31,6 +31,12 @@
     <t>14.07.2026</t>
   </si>
   <si>
+    <t>Дата окончания договора</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Тип договора</t>
   </si>
   <si>
@@ -161,9 +167,6 @@
   </si>
   <si>
     <t>Материал стен</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Год постройки</t>
@@ -719,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B96"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -749,10 +752,10 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -784,55 +787,55 @@
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3">
-        <v>150450</v>
+      <c r="B8" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B9" s="3">
+        <v>150450</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B10">
-        <v>1200</v>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
         <v>400</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="3" t="s">
+    </row>
+    <row r="14" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -870,19 +873,19 @@
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>32</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>34</v>
@@ -901,15 +904,15 @@
         <v>37</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -957,116 +960,118 @@
         <v>50</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="1"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="B32" s="1"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="3"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
@@ -1074,23 +1079,21 @@
       </c>
       <c r="B45" s="3"/>
     </row>
-    <row r="46" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B46" s="1"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" s="3" t="s">
+      <c r="B46" s="3"/>
+    </row>
+    <row r="47" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="B47" s="1"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>80</v>
@@ -1098,7 +1101,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>81</v>
@@ -1106,7 +1109,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>82</v>
@@ -1114,23 +1117,23 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>84</v>
@@ -1138,61 +1141,61 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B58" s="3" t="s">
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="59" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="B59" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B59" s="1"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="3" t="s">
+    </row>
+    <row r="60" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>91</v>
@@ -1200,7 +1203,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>92</v>
@@ -1208,31 +1211,31 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>84</v>
@@ -1240,137 +1243,137 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B71" s="3"/>
-    </row>
-    <row r="72" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B72" s="1"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B73" s="3"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B72" s="3"/>
+    </row>
+    <row r="73" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B74" s="3"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B75" s="3"/>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B76" s="3"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B77" s="3"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B78" s="3"/>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B79" s="3"/>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B80" s="3"/>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B81" s="3"/>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B82" s="3"/>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B83" s="3"/>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B84" s="3"/>
     </row>
-    <row r="85" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B85" s="1"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B86" s="3" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" s="3"/>
+    </row>
+    <row r="86" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="B86" s="1"/>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>96</v>
@@ -1378,7 +1381,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>97</v>
@@ -1386,7 +1389,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>98</v>
@@ -1394,7 +1397,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>99</v>
@@ -1402,7 +1405,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>100</v>
@@ -1410,7 +1413,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>101</v>
@@ -1418,7 +1421,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>102</v>
@@ -1426,7 +1429,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>103</v>
@@ -1434,7 +1437,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>104</v>
@@ -1442,21 +1445,29 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A86:B86"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="B41">

--- a/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
+++ b/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC28C285-4CE6-4DCB-A8DE-DF4189BBAADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Сделка" state="visible" r:id="rId4"/>
+    <sheet name="Сделка" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="93">
   <si>
     <t>СДЕЛКА</t>
   </si>
@@ -34,9 +35,6 @@
     <t>Дата окончания договора</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Тип договора</t>
   </si>
   <si>
@@ -52,9 +50,6 @@
     <t>Количество собственников</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Стоимость USD</t>
   </si>
   <si>
@@ -244,9 +239,6 @@
     <t>Является собственником</t>
   </si>
   <si>
-    <t>Нет</t>
-  </si>
-  <si>
     <t>Номер доверенности</t>
   </si>
   <si>
@@ -256,48 +248,12 @@
     <t>СОБСТВЕННИК №1</t>
   </si>
   <si>
-    <t>Иванов</t>
-  </si>
-  <si>
-    <t>Александр</t>
-  </si>
-  <si>
-    <t>Иванович</t>
-  </si>
-  <si>
-    <t>05.05.1975</t>
-  </si>
-  <si>
-    <t>1234567</t>
-  </si>
-  <si>
-    <t>3050575A001PB1</t>
-  </si>
-  <si>
-    <t>10.03.2018</t>
-  </si>
-  <si>
-    <t>+375291234567</t>
-  </si>
-  <si>
     <t>Доля собственности</t>
   </si>
   <si>
-    <t>1/2</t>
-  </si>
-  <si>
     <t>СОБСТВЕННИК №2</t>
   </si>
   <si>
-    <t>Назаров</t>
-  </si>
-  <si>
-    <t>Игорь</t>
-  </si>
-  <si>
-    <t>Валерьевич</t>
-  </si>
-  <si>
     <t>СОБСТВЕННИК №3</t>
   </si>
   <si>
@@ -335,30 +291,42 @@
   </si>
   <si>
     <t>+375447778899</t>
+  </si>
+  <si>
+    <t>кирпич</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -412,17 +380,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -721,762 +699,714 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B97"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="2" max="2" width="45" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5">
+        <v>46582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="4">
+        <v>150450</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3">
-        <v>150450</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="6">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="B12" s="6">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="3"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="B25" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="B31" s="4">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="B32" s="7"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B33" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="1"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B44" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="B45" s="4"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B46" s="4"/>
+    </row>
+    <row r="47" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="B47" s="7"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="4"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="4"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="4"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="4"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="4"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="4"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="4"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="4"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" s="4"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" s="4"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58" s="4"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="3"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="B59" s="4"/>
+    </row>
+    <row r="60" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B46" s="3"/>
-    </row>
-    <row r="47" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="B60" s="7"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="4"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B62" s="4"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" s="4"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B64" s="4"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B65" s="4"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" s="4"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67" s="4"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B68" s="4"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="4"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="4"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="4"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="4"/>
+    </row>
+    <row r="73" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="B73" s="7"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" s="4"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B75" s="4"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B76" s="4"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B77" s="4"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B78" s="4"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B79" s="4"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80" s="4"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="4"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82" s="4"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B83" s="4"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B84" s="4"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B85" s="4"/>
+    </row>
+    <row r="86" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="7" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="B86" s="7"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="B89" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="B90" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="B91" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="B92" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="B93" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="B94" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+      <c r="B95" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
+      <c r="B96" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="60" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B60" s="1"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B61" s="3" t="s">
+      <c r="B97" s="4" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B72" s="3"/>
-    </row>
-    <row r="73" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B73" s="1"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B74" s="3"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B75" s="3"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B76" s="3"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B77" s="3"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B78" s="3"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B79" s="3"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B80" s="3"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B81" s="3"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B82" s="3"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B83" s="3"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B84" s="3"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B85" s="3"/>
-    </row>
-    <row r="86" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B86" s="1"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A86:B86"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A86:B86"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="B41">
-      <formula1>"Да,Нет"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="B5">
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="B41" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
+++ b/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC28C285-4CE6-4DCB-A8DE-DF4189BBAADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454EEE3C-D094-4E57-85C5-C32A7794A6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="96">
   <si>
     <t>СДЕЛКА</t>
   </si>
@@ -294,6 +294,15 @@
   </si>
   <si>
     <t>кирпич</t>
+  </si>
+  <si>
+    <t>Назаров</t>
+  </si>
+  <si>
+    <t>Игорь</t>
+  </si>
+  <si>
+    <t>Валерьевич</t>
   </si>
 </sst>
 </file>
@@ -1073,67 +1082,89 @@
       <c r="A48" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="4"/>
+      <c r="B48" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="4"/>
+      <c r="B49" s="4" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="4"/>
+      <c r="B50" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="4"/>
+      <c r="B51" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B52" s="4"/>
+      <c r="B52" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="4"/>
+      <c r="B53" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="4"/>
+      <c r="B54" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="4"/>
+      <c r="B55" s="4" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="4"/>
+      <c r="B56" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B57" s="4"/>
+      <c r="B57" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B58" s="4"/>
+      <c r="B58" s="4" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
@@ -1402,7 +1433,7 @@
     <mergeCell ref="A60:B60"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B41" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="B41 B56" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
+++ b/excel/Шаблон_сделки_ГермесГарант_Заполненный.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBCFC5D-5643-4327-8271-38D23ACD3291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Сделка" state="visible" r:id="rId4"/>
+    <sheet name="Сделка" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>СДЕЛКА</t>
   </si>
@@ -22,9 +23,6 @@
     <t>Номер договора</t>
   </si>
   <si>
-    <t>GG-2026-147</t>
-  </si>
-  <si>
     <t>Дата договора</t>
   </si>
   <si>
@@ -40,9 +38,6 @@
     <t>Стоимость USD</t>
   </si>
   <si>
-    <t>105000</t>
-  </si>
-  <si>
     <t>Стоимость BYN</t>
   </si>
   <si>
@@ -139,9 +134,6 @@
     <t>Кадастровый номер</t>
   </si>
   <si>
-    <t>423680100001234</t>
-  </si>
-  <si>
     <t>Инвентарный номер</t>
   </si>
   <si>
@@ -241,15 +233,6 @@
     <t>СОБСТВЕННИК №1</t>
   </si>
   <si>
-    <t>Назаров</t>
-  </si>
-  <si>
-    <t>Игорь</t>
-  </si>
-  <si>
-    <t>Валерьевич</t>
-  </si>
-  <si>
     <t>Доля собственности</t>
   </si>
   <si>
@@ -260,6 +243,21 @@
   </si>
   <si>
     <t>ПОКУПАТЕЛЬ</t>
+  </si>
+  <si>
+    <t>Площадь участка</t>
+  </si>
+  <si>
+    <t>Форма собственности</t>
+  </si>
+  <si>
+    <t>Дополнительные условия</t>
+  </si>
+  <si>
+    <t>50/1</t>
+  </si>
+  <si>
+    <t>Мебель остается</t>
   </si>
   <si>
     <t>Сидоров</t>
@@ -298,19 +296,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -320,12 +318,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
-      <color theme="1"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -379,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -396,9 +394,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -697,39 +706,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B95"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B98"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="45" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1"/>
+      <c r="B1" s="11"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="6">
         <v>46582</v>
@@ -737,7 +746,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
@@ -745,133 +754,127 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="B6" s="9">
+        <v>51834</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>150450</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1200</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>28</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B19" s="4"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>30</v>
@@ -879,547 +882,540 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B29" s="4">
         <v>1998</v>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>47</v>
-      </c>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="4"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>49</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="B31" s="4"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>53</v>
+        <v>77</v>
+      </c>
+      <c r="B32" s="4"/>
+    </row>
+    <row r="33" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B43" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" s="4"/>
-    </row>
-    <row r="45" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>75</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B46" s="4"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>77</v>
+        <v>70</v>
+      </c>
+      <c r="B47" s="4"/>
+    </row>
+    <row r="48" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B49" s="4"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B50" s="4"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>59</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B51" s="4"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>61</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B52" s="4"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>63</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B53" s="4"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B54" s="4"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B55" s="4"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B56" s="4"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B57" s="4"/>
     </row>
-    <row r="58" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>79</v>
-      </c>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="4"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B59" s="4"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B60" s="4"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="4"/>
+    <row r="61" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B62" s="4"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B63" s="4"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B64" s="4"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B65" s="4"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B66" s="4"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B67" s="4"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B68" s="4"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B69" s="4"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B70" s="4"/>
     </row>
-    <row r="71" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>80</v>
-      </c>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="4"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B72" s="4"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B73" s="4"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B74" s="4"/>
+    <row r="74" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B75" s="4"/>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B76" s="4"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B77" s="4"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B78" s="4"/>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B79" s="4"/>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B80" s="4"/>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B81" s="4"/>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B82" s="4"/>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B83" s="4"/>
     </row>
-    <row r="84" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>81</v>
-      </c>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>82</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B85" s="4"/>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>84</v>
+        <v>72</v>
+      </c>
+      <c r="B86" s="4"/>
+    </row>
+    <row r="87" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>85</v>
+        <v>45</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>86</v>
+        <v>47</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>87</v>
+        <v>49</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>88</v>
+        <v>51</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>89</v>
+        <v>53</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>90</v>
+        <v>55</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>91</v>
+        <v>57</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>92</v>
+        <v>59</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="B41">
-      <formula1>"Да,Нет"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="B56">
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="B44 B59" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>